--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484184_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484184_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6321</v>
+        <v>4.528</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9168</v>
+        <v>4.6469</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7154</v>
+        <v>-0.1189</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1253</v>
+        <v>0.862</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6498</v>
+        <v>-0.6757</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4754</v>
+        <v>1.5377</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0825</v>
+        <v>2.3015</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1252</v>
+        <v>-0.156</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0427</v>
+        <v>2.4575</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0428</v>
+        <v>-1.4395</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5246</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5182</v>
+        <v>-0.9198</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2174</v>
+        <v>1.0033</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0463</v>
+        <v>0.873</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1711</v>
+        <v>0.1303</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9449</v>
+        <v>1.4724</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9449</v>
+        <v>1.4724</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5372</v>
+        <v>3.3659</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7684</v>
+        <v>2.8971</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2311</v>
+        <v>0.4687</v>
       </c>
       <c r="G3" t="n">
-        <v>0.862</v>
+        <v>2.1628</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6757</v>
+        <v>0.2466</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5377</v>
+        <v>1.9162</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3015</v>
+        <v>2.999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.156</v>
+        <v>0.4287</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4575</v>
+        <v>2.5703</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4395</v>
+        <v>-0.8363</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1821</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9198</v>
+        <v>-0.6542</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0125</v>
+        <v>0.8063</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0056</v>
+        <v>0.89</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0181</v>
+        <v>-0.0837</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3775</v>
+        <v>3.3273</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7488</v>
+        <v>3.0609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6287</v>
+        <v>0.2665</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4692</v>
+        <v>-1.1253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4234</v>
+        <v>-0.6498</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0458</v>
+        <v>-0.4754</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8973</v>
+        <v>-0.0825</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8774999999999999</v>
+        <v>-0.1252</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0198</v>
+        <v>0.0427</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4281</v>
+        <v>-1.0428</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4542</v>
+        <v>-0.5246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.026</v>
+        <v>-0.5182</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.9126</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5613</v>
+        <v>1.1904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4626</v>
+        <v>-0.2778</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.9449</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>2.9449</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3215</v>
+        <v>2.6898</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2017</v>
+        <v>2.1172</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1198</v>
+        <v>0.5726</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2136</v>
+        <v>3.4692</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3487</v>
+        <v>0.4234</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5623</v>
+        <v>3.0458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4801</v>
+        <v>3.8973</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3947</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0854</v>
+        <v>3.0198</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6937</v>
+        <v>-0.4281</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.046</v>
+        <v>-0.4542</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>1.527</v>
+        <v>0.411</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4989</v>
+        <v>0.9297</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0281</v>
+        <v>-0.5187</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0307</v>
+        <v>1.7807</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8145</v>
+        <v>-0.0024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2162</v>
+        <v>1.7831</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1628</v>
+        <v>-0.2136</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2466</v>
+        <v>0.3487</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9162</v>
+        <v>-0.5623</v>
       </c>
       <c r="J6" t="n">
-        <v>2.999</v>
+        <v>0.4801</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4287</v>
+        <v>0.3947</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5703</v>
+        <v>0.0854</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8363</v>
+        <v>-0.6937</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1821</v>
+        <v>-0.046</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6542</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5288</v>
+        <v>0.9862</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1926</v>
+        <v>0.2948</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3362</v>
+        <v>0.6914</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4033</v>
+        <v>0.3448</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1064</v>
+        <v>-0.002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5097</v>
+        <v>0.3468</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.1416</v>
+        <v>0.4029</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4237</v>
+        <v>-0.0454</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7179</v>
+        <v>0.4483</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.3248</v>
+        <v>0.0603</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6497</v>
+        <v>0.0202</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6751</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8168</v>
+        <v>0.3425</v>
       </c>
       <c r="N7" t="n">
-        <v>0.226</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0428</v>
+        <v>0.4081</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9758</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9758</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3032</v>
+        <v>-0.0581</v>
       </c>
       <c r="T7" t="n">
-        <v>1.746</v>
+        <v>-0.0623</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4428</v>
+        <v>0.0042</v>
       </c>
       <c r="V7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1982</v>
+        <v>0.1915</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0644</v>
+        <v>-0.2062</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2626</v>
+        <v>0.3977</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4029</v>
+        <v>-1.4215</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0454</v>
+        <v>0.0554</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4483</v>
+        <v>-1.4769</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0603</v>
+        <v>-0.1837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0202</v>
+        <v>0.3735</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>-0.5572</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3425</v>
+        <v>-1.2379</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.3181</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4081</v>
+        <v>-0.9198</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2046</v>
+        <v>0.4308</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1247</v>
+        <v>-0.0226</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0799</v>
+        <v>0.4534</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.3287</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9204</v>
+        <v>-0.9226</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3977</v>
+        <v>0.5939</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4215</v>
+        <v>-4.1416</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0554</v>
+        <v>-2.4237</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4769</v>
+        <v>-1.7179</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1837</v>
+        <v>-3.3248</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3735</v>
+        <v>-2.6497</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5572</v>
+        <v>-0.6751</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2379</v>
+        <v>-0.8168</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3181</v>
+        <v>0.226</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9198</v>
+        <v>-1.0428</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7855</v>
+        <v>2.9758</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>2.9758</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2834</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7368</v>
+        <v>0.9297</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4534</v>
+        <v>-0.3586</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7052</v>
+        <v>-0.8889</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4939</v>
+        <v>-1.902</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7887</v>
+        <v>1.0131</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3092</v>
@@ -1234,13 +1234,13 @@
         <v>2.1822</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0544</v>
+        <v>-0.238</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5103</v>
+        <v>0.1021</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5646</v>
+        <v>-0.3402</v>
       </c>
       <c r="V10" t="n">
         <v>-0.532</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3169</v>
+        <v>-1.1511</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7108</v>
+        <v>-1.4047</v>
       </c>
       <c r="F11" t="n">
-        <v>0.394</v>
+        <v>0.2537</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2168</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0822</v>
+        <v>0.248</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3741</v>
+        <v>-0.068</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4562</v>
+        <v>0.316</v>
       </c>
       <c r="V11" t="n">
         <v>1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6327</v>
+        <v>-3.2245</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0829</v>
+        <v>-1.8992</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5498</v>
+        <v>-1.3254</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9104</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9603</v>
+        <v>0.3685</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3151</v>
+        <v>0.4989</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3549</v>
+        <v>-0.1304</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2777</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.323</v>
+        <v>10.6348</v>
       </c>
       <c r="E13" t="n">
-        <v>6.071400000000001</v>
+        <v>6.383000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2519</v>
+        <v>4.251799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.441500000000001</v>
+        <v>-5.4415</v>
       </c>
       <c r="H13" t="n">
         <v>-5.4415</v>
       </c>
       <c r="I13" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>0.0001000000000004331</v>
       </c>
       <c r="J13" t="n">
         <v>3.240699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>16.8629</v>
       </c>
       <c r="S13" t="n">
-        <v>5.13</v>
+        <v>5.441700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2441</v>
+        <v>5.5557</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1140999999999999</v>
+        <v>-0.1141</v>
       </c>
       <c r="V13" t="n">
         <v>4.6834</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3506</v>
+        <v>2.1741</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2408</v>
+        <v>2.8407</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8902</v>
+        <v>-0.6666</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9897</v>
+        <v>0.639</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0259</v>
+        <v>0.157</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0362</v>
+        <v>0.4819</v>
       </c>
       <c r="J14" t="n">
-        <v>2.749</v>
+        <v>0.6297</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8655</v>
+        <v>-0.6229</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8836000000000001</v>
+        <v>1.2527</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7593</v>
+        <v>0.0092</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1605</v>
+        <v>0.78</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9198</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4446</v>
+        <v>-0.2069</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8885</v>
+        <v>0.3175</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4439</v>
+        <v>-0.5245</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6789</v>
+        <v>1.5437</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6789</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.203</v>
+        <v>1.5314</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6367</v>
+        <v>0.4466</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4337</v>
+        <v>1.0848</v>
       </c>
       <c r="G15" t="n">
-        <v>0.639</v>
+        <v>3.3825</v>
       </c>
       <c r="H15" t="n">
-        <v>0.157</v>
+        <v>2.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4819</v>
+        <v>1.3525</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6297</v>
+        <v>3.3093</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6229</v>
+        <v>1.4516</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2527</v>
+        <v>1.8576</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0092</v>
+        <v>0.0732</v>
       </c>
       <c r="N15" t="n">
-        <v>0.78</v>
+        <v>0.5784</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5051</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3887</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1781</v>
+        <v>-0.9268</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1135</v>
+        <v>0.0455</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2916</v>
+        <v>-0.9722</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5437</v>
+        <v>0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2821</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3267</v>
+        <v>1.1864</v>
       </c>
       <c r="E16" t="n">
         <v>0.9983</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3284</v>
+        <v>0.1881</v>
       </c>
       <c r="G16" t="n">
         <v>1.0575</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1276</v>
+        <v>-0.2678</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1218</v>
+        <v>-0.0185</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.591</v>
+        <v>0.7378</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1656</v>
+        <v>3.384</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7566000000000001</v>
+        <v>-2.6462</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3825</v>
+        <v>1.9897</v>
       </c>
       <c r="H17" t="n">
-        <v>2.03</v>
+        <v>2.0259</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3525</v>
+        <v>-0.0362</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3093</v>
+        <v>2.749</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4516</v>
+        <v>1.8655</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8576</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0732</v>
+        <v>-0.7593</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5784</v>
+        <v>0.1605</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5051</v>
+        <v>-0.9198</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1741</v>
+        <v>-0.3968</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8671</v>
+        <v>0.8318</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5667</v>
+        <v>1.0317</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3004</v>
+        <v>-0.1999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.266</v>
+        <v>-2.6789</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2074</v>
+        <v>0.4592</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8062</v>
+        <v>-0.5001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5988</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>2.0912</v>
@@ -1858,13 +1858,13 @@
         <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4374</v>
+        <v>-0.7709</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1926</v>
+        <v>0.1135</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2448</v>
+        <v>-0.8843</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6783</v>
+        <v>-1.6145</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3297</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1445</v>
+        <v>-1.2848</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5629</v>
@@ -1936,13 +1936,13 @@
         <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1786</v>
+        <v>-0.1148</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3202</v>
+        <v>0.1799</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1352</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0865</v>
+        <v>-1.7524</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0859</v>
+        <v>-2.7798</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9993</v>
+        <v>1.0274</v>
       </c>
       <c r="G20" t="n">
         <v>-1.102</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5878</v>
+        <v>-0.2537</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4364</v>
+        <v>-0.1303</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1514</v>
+        <v>-0.1233</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6068</v>
+        <v>-2.0788</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2791</v>
+        <v>-0.6669</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3276</v>
+        <v>-1.4118</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2332</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1671</v>
+        <v>-0.6391</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7481</v>
+        <v>-0.136</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.419</v>
+        <v>-0.5031</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1571</v>
+        <v>-4.4421</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8736</v>
+        <v>-2.7716</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2835</v>
+        <v>-1.6705</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4823</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0877</v>
+        <v>-0.3727</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3173</v>
+        <v>-0.2153</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7704</v>
+        <v>-0.1574</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0583</v>
+        <v>-5.1639</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3835</v>
+        <v>-4.8734</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6748</v>
+        <v>-0.2905</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3379</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9431</v>
+        <v>-1.0486</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8784</v>
+        <v>-0.3683</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0646</v>
+        <v>-0.6803</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.3231</v>
+        <v>-8.9628</v>
       </c>
       <c r="E24" t="n">
         <v>-4.251899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.0712</v>
+        <v>-4.710899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>5.441599999999999</v>
@@ -2296,7 +2296,7 @@
         <v>5.4415</v>
       </c>
       <c r="I24" t="n">
-        <v>9.999999999988143e-05</v>
+        <v>0.0001000000000003255</v>
       </c>
       <c r="J24" t="n">
         <v>8.682500000000001</v>
@@ -2326,13 +2326,13 @@
         <v>10.9112</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.1299</v>
+        <v>-3.7695</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1142999999999998</v>
+        <v>0.1142</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.2441</v>
+        <v>-3.883599999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-4.6834</v>
